--- a/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/practice_start.xlsx
@@ -455,8 +455,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -516,12 +516,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
